--- a/docs/addendum_AI_list.xlsx
+++ b/docs/addendum_AI_list.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12465" windowHeight="10920" activeTab="1"/>
+    <workbookView windowWidth="12465" windowHeight="10920"/>
   </bookViews>
   <sheets>
     <sheet name="AI清单" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="453">
   <si>
     <t>类别</t>
   </si>
@@ -1021,6 +1021,12 @@
     <t>肌无力肌萎缩肌纤维化</t>
   </si>
   <si>
+    <t>四肢慢慢慢慢无力，四肢肌肉慢慢慢慢萎缩，最后连话都说不出来，浑身的肌肉都没劲，饭也吃不下去了。</t>
+  </si>
+  <si>
+    <t>四肢的病中间治，找肚脐。补脾的同时一定要补肾，所以灸肚脐+补肾三针。</t>
+  </si>
+  <si>
     <t>大脑炎</t>
   </si>
   <si>
@@ -1070,7 +1076,7 @@
     <t>四肢</t>
   </si>
   <si>
-    <t>治了三个月，基本上正常了。 还没完全根治，他另外一个女儿又生孩子了，他跑去带孙子了。</t>
+    <t>四肢的病中间治。那会儿我没给他灸，我就是揉他的肚子。揉了三个月，基本上正常了。 还没完全根治，他另外一个女儿又生孩子了，他跑去带孙子了。</t>
   </si>
   <si>
     <t>肌肉萎缩</t>
@@ -1104,6 +1110,253 @@
   </si>
   <si>
     <t>脾开窍于口，其华在唇</t>
+  </si>
+  <si>
+    <t>嘴角烂了，嘴唇干裂，痛，痒</t>
+  </si>
+  <si>
+    <t>唇</t>
+  </si>
+  <si>
+    <t>历兑</t>
+  </si>
+  <si>
+    <t>或吃牛黄清胃丸</t>
+  </si>
+  <si>
+    <t>鼻头上长一大痤疮。大脓疙瘩，而且鼻子头整个是红的。</t>
+  </si>
+  <si>
+    <t>隐白</t>
+  </si>
+  <si>
+    <t>隐白放血。放完血第二天就瘪了，红去掉一大半，我说接着放，放的血还不够。放两天，完全好了。</t>
+  </si>
+  <si>
+    <t>两颐是红的，有时候是红得发紫，上面有很多小疙瘩</t>
+  </si>
+  <si>
+    <t>两颐</t>
+  </si>
+  <si>
+    <t>腘窝</t>
+  </si>
+  <si>
+    <t>用梅花针，玩命的敲腘窝，敲完之后咣拔一罐，血一出来，两颐立刻就好。</t>
+  </si>
+  <si>
+    <t>腿沉，走不动路</t>
+  </si>
+  <si>
+    <t>轻轻一摁奇痛无比</t>
+  </si>
+  <si>
+    <t>揉胯骨沿儿揉到不痛，腿就不沉了</t>
+  </si>
+  <si>
+    <t>脸肿，额上一按一个坑，脸肿了20年了</t>
+  </si>
+  <si>
+    <t>揉胯骨沿儿20分钟，揉到不痛，脸肿立刻消失。</t>
+  </si>
+  <si>
+    <t>脚气，脚痒</t>
+  </si>
+  <si>
+    <t>揉胯骨沿儿揉到不痛，脚立刻不痒了。</t>
+  </si>
+  <si>
+    <t>落枕，脖子强痛，转不动</t>
+  </si>
+  <si>
+    <t>揉胯骨沿儿揉到不痛，再在肩中带点一点，脖子就好了。</t>
+  </si>
+  <si>
+    <t>膝盖肿痛，肿里头有积液，叫关节腔积液。</t>
+  </si>
+  <si>
+    <t>腹股沟、伏兔</t>
+  </si>
+  <si>
+    <t>揉两三次它那个水就下去了，很简单。</t>
+  </si>
+  <si>
+    <t>天枢、中脘
+内庭、历兑
+丰隆</t>
+  </si>
+  <si>
+    <t>扎针</t>
+  </si>
+  <si>
+    <t>头天还好好的，第二天早上，（右）胳膊整条胳膊肿，又肿又疼</t>
+  </si>
+  <si>
+    <t>右胳膊</t>
+  </si>
+  <si>
+    <t>左腿脾经</t>
+  </si>
+  <si>
+    <t>梅花针敲</t>
+  </si>
+  <si>
+    <t>从（左）大腿根这用梅花针敲，敲脾经，我不知道治哪，但我知道是脾的问题，足矣。敲脾经一直敲到隐白。敲完一遍再敲一遍。就这么一遍一遍敲，敲了3、4遍之后，也就十几分钟吧，那胳膊扑哧一下瘪了。</t>
+  </si>
+  <si>
+    <t>眼袋</t>
+  </si>
+  <si>
+    <t>公孙</t>
+  </si>
+  <si>
+    <t>脾经公孙穴，扎上之后五六分钟，扑，（眼袋）瘪了。</t>
+  </si>
+  <si>
+    <t>肚子胀得难受</t>
+  </si>
+  <si>
+    <t>手三里、飞扬</t>
+  </si>
+  <si>
+    <t>扎完（左）手三里，深浅没扎到位。再扎（右）飞扬，这针的深浅扎到位了。病人自陈，（右侧）这里边哗就下去了，这边（左边）就没动。（左）手三里重扎一下，一扎到位，扑，那气就下去了。</t>
+  </si>
+  <si>
+    <t>一个老太太，（左）屁股蛋整个瘪，右边正常，瘪了30年，而且左腿非常痛，膏药贴满腿。</t>
+  </si>
+  <si>
+    <t>左肩中带</t>
+  </si>
+  <si>
+    <t>一碰奇痛</t>
+  </si>
+  <si>
+    <t>就把这肩中带一揉，一次之后，他就再也没疼过。揉三次之后，鼓起来了。</t>
+  </si>
+  <si>
+    <t>小儿感冒发烧</t>
+  </si>
+  <si>
+    <t>脊</t>
+  </si>
+  <si>
+    <t>捏</t>
+  </si>
+  <si>
+    <t>一天捏一次也好，捏两次也好。但是每次必须是三遍。对孩子脾胃虚弱体弱多病治疗效果很好。捏脊之后，积食去掉，烧就会退。</t>
+  </si>
+  <si>
+    <t>小儿各种病</t>
+  </si>
+  <si>
+    <t>粘肌</t>
+  </si>
+  <si>
+    <t>粘肚子称为粘肌，是我们的祖传绝招。粘肌很痛的，一定要摁住他，痛也得粘，一直粘到不痛。能粘出各种颜色的东西来，黄的，白的，水湿的，黑的，粘出什么来都是好的。蜂蜜解百毒。</t>
+  </si>
+  <si>
+    <t>五岁小孩浑身痒，越到晚上越痒</t>
+  </si>
+  <si>
+    <t>粘完了之后就好了80%，白天不痒，就到晚上还有点痒，也很轻了。就一次。不过他那一次太狠，他给粘了40分钟，把那孩子痛得哭得哇哇叫。第二次再粘，不让了，没粘成。</t>
+  </si>
+  <si>
+    <t>癌症，开过四回刀了，满肚子疼疼得不行，吃什么药都不管用。</t>
+  </si>
+  <si>
+    <t>就粘了一次，肚子就不疼了。</t>
+  </si>
+  <si>
+    <t>肚子胀得非常厉害，用其他方法都试过了，都不好</t>
+  </si>
+  <si>
+    <t>粘完一回，肚子没动静。歇一会儿，又涂又粘，粘完第二回，肚子软和点了。再歇一会儿，又涂又粘，粘完第三回，肚子扑哧下去了。但粘的人趴下了，浑身没劲，歇了两天。</t>
+  </si>
+  <si>
+    <t>舌尖是平的，舌头吐不出来</t>
+  </si>
+  <si>
+    <t>耳鸣</t>
+  </si>
+  <si>
+    <t>耳</t>
+  </si>
+  <si>
+    <t>肾、心</t>
+  </si>
+  <si>
+    <t>肘窝</t>
+  </si>
+  <si>
+    <t>拍</t>
+  </si>
+  <si>
+    <t>先补肾吃一个月六味地黄丸，然后拍肘窝。把肾水补足了再降心火。20年耳鸣，吃了一车六味地黄了，还没好，我说你过来我打你一顿，拍胳膊肘，拍完了，他说好了80%。我说你这时间太长了，你过两天再拍。</t>
+  </si>
+  <si>
+    <t>中耳炎，耳朵里头发炎化脓，疼痛得很难受，特别难治。</t>
+  </si>
+  <si>
+    <t>肘窝
+或中指小指四缝的瘀络</t>
+  </si>
+  <si>
+    <t>血一出来，耳朵马上就不痛了。然后补肾。</t>
+  </si>
+  <si>
+    <t>急性耳聋</t>
+  </si>
+  <si>
+    <t>耳背</t>
+  </si>
+  <si>
+    <t>飞蚊症，眼前一个黑影或者干脆就堵一块儿，有一块看东西是黑的</t>
+  </si>
+  <si>
+    <t>目</t>
+  </si>
+  <si>
+    <t>心经</t>
+  </si>
+  <si>
+    <t>心经上有一条硬结</t>
+  </si>
+  <si>
+    <t>把心经上的硬结拔开，也就用了15分钟，黑影没了。</t>
+  </si>
+  <si>
+    <t>眼结膜炎。眼睛红、发痛。吃龙胆泻肝丸，或黄连羊肝丸，吃半天不好。</t>
+  </si>
+  <si>
+    <t>中指指腹</t>
+  </si>
+  <si>
+    <t>吃清心明目上清丸。外加放血。在中指上画一小人，你找那两个眼睛的位置，放两针血。这个心火就下来了。</t>
+  </si>
+  <si>
+    <t>眼睛的病</t>
+  </si>
+  <si>
+    <t>把脖子上的结揉开，把眼点的结揉开，眼睛就好了。</t>
+  </si>
+  <si>
+    <t>大腿脾经上发现一个非常黑的瘀络</t>
+  </si>
+  <si>
+    <t>当时流了好多血。放完血之后，吃完饭就困的毛病没了。</t>
+  </si>
+  <si>
+    <t>脉管炎。脚冷、麻、刺痛或烧灼。</t>
+  </si>
+  <si>
+    <t>宗筋、脖子</t>
+  </si>
+  <si>
+    <t>吃龙胆泻肝丸。然后隔两天揉一次，揉了不到三个月，好了。
+还可以放血，放大指小指的血，在胆经上找瘀络放血。</t>
+  </si>
+  <si>
+    <t>心主神志</t>
   </si>
   <si>
     <t>刮痧</t>
@@ -1142,9 +1395,6 @@
     <t>把结揉开。如果一次不能揉开，就多揉几次。揉到结节的时候会很痛，就把力停在那，揉到不痛，结节就揉散了。也有摸到结节不痛的，从不痛揉到痛，再从痛揉到不痛。问：揉到的结节会不会是淋巴结？
 师答：淋巴结平常它很小，它不发炎的时候它不会长大。所以不可能揉到淋巴结。
 宗筋处的结节，肘下都会感觉到，咯噔咯噔的，揉时很痛，揉到不痛，结节就散了。</t>
-  </si>
-  <si>
-    <t>扎针</t>
   </si>
   <si>
     <t>故诸刺络脉者，必刺其结上。盛血虽无结，必刺其血出其邪。</t>
@@ -2122,8 +2372,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:J100"/>
+  <sheetPr/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25"/>
   <cols>
     <col min="1" max="1" width="7.625" style="1" customWidth="1"/>
@@ -2171,7 +2421,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:10">
+    <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
@@ -2195,7 +2445,7 @@
       </c>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" hidden="1" spans="1:10">
+    <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -2243,7 +2493,7 @@
       </c>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" hidden="1" spans="1:10">
+    <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -2323,7 +2573,7 @@
       </c>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" hidden="1" spans="1:10">
+    <row r="8" spans="1:10">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>38</v>
@@ -2345,7 +2595,7 @@
       </c>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" ht="40.5" hidden="1" spans="1:10">
+    <row r="9" ht="40.5" spans="1:10">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -2373,7 +2623,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:10">
+    <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
@@ -2445,7 +2695,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:10">
+    <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
         <v>10</v>
       </c>
@@ -2545,7 +2795,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" ht="40.5" hidden="1" spans="1:10">
+    <row r="17" ht="40.5" spans="1:10">
       <c r="A17" s="4" t="s">
         <v>10</v>
       </c>
@@ -2573,7 +2823,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:10">
+    <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
         <v>10</v>
       </c>
@@ -2629,7 +2879,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="1:10">
+    <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
         <v>10</v>
       </c>
@@ -2683,7 +2933,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" ht="40.5" hidden="1" spans="1:10">
+    <row r="22" ht="40.5" spans="1:10">
       <c r="A22" s="4" t="s">
         <v>10</v>
       </c>
@@ -2707,7 +2957,7 @@
       </c>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" ht="60.75" hidden="1" spans="1:10">
+    <row r="23" ht="60.75" spans="1:10">
       <c r="A23" s="4" t="s">
         <v>10</v>
       </c>
@@ -2761,7 +3011,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" ht="40.5" hidden="1" spans="1:10">
+    <row r="25" ht="40.5" spans="1:10">
       <c r="A25" s="4" t="s">
         <v>44</v>
       </c>
@@ -2789,7 +3039,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="26" ht="60.75" hidden="1" spans="1:10">
+    <row r="26" ht="60.75" spans="1:10">
       <c r="A26" s="4" t="s">
         <v>44</v>
       </c>
@@ -2905,7 +3155,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="30" ht="40.5" hidden="1" spans="1:10">
+    <row r="30" ht="40.5" spans="1:10">
       <c r="A30" s="4" t="s">
         <v>10</v>
       </c>
@@ -2935,7 +3185,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="31" ht="81" hidden="1" spans="1:10">
+    <row r="31" ht="81" spans="1:10">
       <c r="A31" s="4" t="s">
         <v>10</v>
       </c>
@@ -2965,7 +3215,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="32" ht="60.75" hidden="1" spans="1:10">
+    <row r="32" ht="60.75" spans="1:10">
       <c r="A32" s="4" t="s">
         <v>10</v>
       </c>
@@ -2993,7 +3243,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="33" ht="60.75" hidden="1" spans="1:10">
+    <row r="33" ht="60.75" spans="1:10">
       <c r="A33" s="4" t="s">
         <v>10</v>
       </c>
@@ -3021,7 +3271,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="34" hidden="1" spans="1:10">
+    <row r="34" spans="1:10">
       <c r="A34" s="4" t="s">
         <v>10</v>
       </c>
@@ -3043,7 +3293,7 @@
       </c>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" hidden="1" spans="1:10">
+    <row r="35" spans="1:10">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
         <v>153</v>
@@ -3071,7 +3321,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="36" hidden="1" spans="1:10">
+    <row r="36" spans="1:10">
       <c r="A36" s="4" t="s">
         <v>10</v>
       </c>
@@ -3097,7 +3347,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:10">
+    <row r="37" spans="1:10">
       <c r="A37" s="4" t="s">
         <v>10</v>
       </c>
@@ -3119,7 +3369,7 @@
       </c>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" ht="60.75" hidden="1" spans="1:10">
+    <row r="38" ht="60.75" spans="1:10">
       <c r="A38" s="4" t="s">
         <v>10</v>
       </c>
@@ -3355,7 +3605,7 @@
       </c>
       <c r="J46" s="4"/>
     </row>
-    <row r="47" ht="60.75" hidden="1" spans="1:10">
+    <row r="47" ht="60.75" spans="1:10">
       <c r="A47" s="4" t="s">
         <v>10</v>
       </c>
@@ -3461,7 +3711,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:10">
+    <row r="51" spans="1:10">
       <c r="A51" s="1" t="s">
         <v>10</v>
       </c>
@@ -3487,7 +3737,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:10">
+    <row r="52" spans="1:10">
       <c r="A52" s="1" t="s">
         <v>44</v>
       </c>
@@ -3510,7 +3760,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="53" hidden="1" spans="1:10">
+    <row r="53" spans="1:10">
       <c r="A53" s="1" t="s">
         <v>44</v>
       </c>
@@ -3579,7 +3829,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="1:10">
+    <row r="56" spans="1:10">
       <c r="A56" s="1" t="s">
         <v>10</v>
       </c>
@@ -3605,7 +3855,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="1:10">
+    <row r="57" spans="1:10">
       <c r="A57" s="1" t="s">
         <v>10</v>
       </c>
@@ -3628,7 +3878,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="1:10">
+    <row r="58" spans="1:10">
       <c r="A58" s="1" t="s">
         <v>10</v>
       </c>
@@ -3717,7 +3967,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="62" ht="40.5" hidden="1" spans="1:10">
+    <row r="62" ht="40.5" spans="1:10">
       <c r="A62" s="1" t="s">
         <v>10</v>
       </c>
@@ -3740,7 +3990,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:10">
+    <row r="63" spans="1:10">
       <c r="A63" s="1" t="s">
         <v>10</v>
       </c>
@@ -3766,7 +4016,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="1:10">
+    <row r="64" spans="1:10">
       <c r="A64" s="1" t="s">
         <v>10</v>
       </c>
@@ -3812,7 +4062,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="1:10">
+    <row r="66" spans="1:10">
       <c r="C66" s="1" t="s">
         <v>244</v>
       </c>
@@ -3835,7 +4085,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:10">
+    <row r="67" spans="1:10">
       <c r="A67" s="1" t="s">
         <v>10</v>
       </c>
@@ -3887,7 +4137,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="69" ht="60.75" hidden="1" spans="1:10">
+    <row r="69" ht="60.75" spans="1:10">
       <c r="F69" s="1" t="s">
         <v>252</v>
       </c>
@@ -3947,7 +4197,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="72" hidden="1" spans="1:10">
+    <row r="72" spans="1:10">
       <c r="A72" s="1" t="s">
         <v>10</v>
       </c>
@@ -3970,7 +4220,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="73" ht="60.75" hidden="1" spans="1:10">
+    <row r="73" ht="60.75" spans="1:10">
       <c r="C73" s="1" t="s">
         <v>264</v>
       </c>
@@ -4036,7 +4286,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="76" ht="40.5" hidden="1" spans="1:10">
+    <row r="76" ht="40.5" spans="1:10">
       <c r="A76" s="1" t="s">
         <v>10</v>
       </c>
@@ -4056,7 +4306,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:10">
+    <row r="77" spans="1:10">
       <c r="A77" s="1" t="s">
         <v>10</v>
       </c>
@@ -4082,7 +4332,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="78" ht="60.75" hidden="1" spans="1:10">
+    <row r="78" ht="60.75" spans="1:10">
       <c r="A78" s="1" t="s">
         <v>10</v>
       </c>
@@ -4102,7 +4352,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="79" ht="60.75" hidden="1" spans="1:10">
+    <row r="79" ht="60.75" spans="1:10">
       <c r="A79" s="1" t="s">
         <v>10</v>
       </c>
@@ -4220,7 +4470,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:10">
+    <row r="84" spans="1:10">
       <c r="A84" s="1" t="s">
         <v>10</v>
       </c>
@@ -4249,7 +4499,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="85" ht="60.75" hidden="1" spans="1:10">
+    <row r="85" ht="60.75" spans="1:10">
       <c r="A85" s="1" t="s">
         <v>10</v>
       </c>
@@ -4364,7 +4614,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="90" ht="141.75" hidden="1" spans="1:10">
+    <row r="90" ht="141.75" spans="1:10">
       <c r="A90" s="1" t="s">
         <v>10</v>
       </c>
@@ -4419,13 +4669,16 @@
         <v>326</v>
       </c>
     </row>
-    <row r="92" ht="101.25" spans="1:10">
+    <row r="92" ht="121.5" spans="1:10">
       <c r="A92" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>327</v>
       </c>
+      <c r="C92" s="1" t="s">
+        <v>328</v>
+      </c>
       <c r="E92" s="1" t="s">
         <v>34</v>
       </c>
@@ -4435,16 +4688,19 @@
       <c r="I92" s="1" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="93" ht="121.5" hidden="1" spans="1:10">
+      <c r="J92" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="93" ht="121.5" spans="1:10">
       <c r="A93" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>44</v>
@@ -4453,21 +4709,21 @@
         <v>23</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>194</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="94" ht="40.5" hidden="1" spans="1:10">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="94" ht="40.5" spans="1:10">
       <c r="A94" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>44</v>
@@ -4476,13 +4732,13 @@
         <v>23</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="95" ht="141.75" spans="1:10">
@@ -4493,7 +4749,7 @@
         <v>76</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>155</v>
@@ -4502,16 +4758,16 @@
         <v>34</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="96" ht="121.5" spans="1:10">
@@ -4519,25 +4775,25 @@
         <v>19</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>93</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="97" ht="81" spans="1:10">
@@ -4545,10 +4801,10 @@
         <v>19</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>139</v>
@@ -4560,13 +4816,13 @@
         <v>113</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>262</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="98" ht="40.5" spans="1:10">
@@ -4574,13 +4830,13 @@
         <v>19</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>34</v>
@@ -4589,10 +4845,10 @@
         <v>113</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="99" ht="40.5" spans="1:10">
@@ -4600,36 +4856,623 @@
         <v>19</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="100" ht="40.5" hidden="1" spans="1:10">
+    <row r="100" ht="40.5" spans="1:10">
       <c r="C100" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
+      </c>
+    </row>
+    <row r="101" ht="40.5" spans="1:10">
+      <c r="A101" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="102" ht="60.75" spans="1:10">
+      <c r="A102" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="103" ht="60.75" spans="1:10">
+      <c r="A103" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="104" ht="40.5" spans="1:10">
+      <c r="A104" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="105" ht="40.5" spans="1:10">
+      <c r="A105" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="106" ht="40.5" spans="1:10">
+      <c r="A106" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="107" ht="40.5" spans="1:10">
+      <c r="A107" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="108" ht="60.75" spans="1:10">
+      <c r="A108" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="109" ht="60.75" spans="1:10">
+      <c r="A109" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="110" ht="141.75" spans="1:10">
+      <c r="A110" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="111" ht="40.5" spans="1:10">
+      <c r="A111" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="112" ht="121.5" spans="1:10">
+      <c r="A112" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="113" ht="101.25" spans="1:10">
+      <c r="A113" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="114" ht="81" spans="1:10">
+      <c r="A114" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="115" ht="121.5" spans="1:10">
+      <c r="A115" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="116" ht="121.5" spans="1:10">
+      <c r="A116" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="117" ht="81" spans="1:10">
+      <c r="A117" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="118" ht="121.5" spans="1:10">
+      <c r="A118" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="119" ht="40.5" spans="1:10">
+      <c r="C119" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="120" ht="141.75" spans="1:10">
+      <c r="A120" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="121" ht="60.75" spans="1:10">
+      <c r="A121" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="122" ht="60.75" spans="1:10">
+      <c r="A122" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="123" ht="60.75" spans="1:10">
+      <c r="A123" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="124" ht="81" spans="1:10">
+      <c r="A124" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="125" ht="81" spans="1:10">
+      <c r="A125" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="126" ht="40.5" spans="1:10">
+      <c r="A126" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="127" ht="40.5" spans="1:10">
+      <c r="A127" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="128" ht="81" spans="1:10">
+      <c r="A128" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="129" spans="3:3">
+      <c r="C129" s="1" t="s">
+        <v>437</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J100" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="0">
-      <customFilters>
-        <customFilter operator="equal" val="内科"/>
-      </customFilters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4653,26 +5496,26 @@
         <v>93</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>355</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>356</v>
+        <v>439</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>357</v>
+        <v>440</v>
       </c>
       <c r="C2" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>358</v>
+        <v>441</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>359</v>
+        <v>442</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -4686,7 +5529,7 @@
         <v>140</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>360</v>
+        <v>443</v>
       </c>
       <c r="C4" s="2">
         <v>4</v>
@@ -4712,40 +5555,40 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="B1" s="1" t="s">
-        <v>361</v>
+        <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>356</v>
+        <v>439</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>362</v>
+        <v>445</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>363</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3" ht="141.75" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>364</v>
+        <v>447</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>365</v>
+        <v>448</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>366</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>365</v>
+        <v>448</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>368</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4753,10 +5596,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>369</v>
+        <v>451</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>370</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>

--- a/docs/addendum_AI_list.xlsx
+++ b/docs/addendum_AI_list.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12465" windowHeight="10920"/>
+    <workbookView windowWidth="12465" windowHeight="10920" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="AI清单" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="核心奥义" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AI清单!$A$1:$J$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AI清单!$A$1:$J$129</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="455">
   <si>
     <t>类别</t>
   </si>
@@ -1375,6 +1375,12 @@
   </si>
   <si>
     <t>左五枢有强烈压痛，深处有一个蚕豆大软结。平时少有微隐痛</t>
+  </si>
+  <si>
+    <t>综合</t>
+  </si>
+  <si>
+    <t>胆经</t>
   </si>
   <si>
     <t>核心奥义</t>
@@ -5472,7 +5478,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J100" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J129" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5483,8 +5489,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12.375" style="2" customWidth="1"/>
     <col min="2" max="2" width="68.625" style="2" customWidth="1"/>
@@ -5507,7 +5513,7 @@
         <v>440</v>
       </c>
       <c r="C2" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5532,7 +5538,20 @@
         <v>443</v>
       </c>
       <c r="C4" s="2">
-        <v>4</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -5555,7 +5574,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="B1" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5563,21 +5582,21 @@
         <v>439</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" ht="141.75" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5585,10 +5604,10 @@
         <v>381</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5596,10 +5615,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>

--- a/docs/addendum_AI_list.xlsx
+++ b/docs/addendum_AI_list.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12465" windowHeight="10920" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="AI清单" sheetId="1" r:id="rId1"/>
@@ -2384,7 +2384,7 @@
   <cols>
     <col min="1" max="1" width="7.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.75" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="8.75" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.25" style="1" customWidth="1"/>

--- a/docs/addendum_AI_list.xlsx
+++ b/docs/addendum_AI_list.xlsx
@@ -12,7 +12,7 @@
     <sheet name="核心奥义" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AI清单!$A$1:$J$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AI清单!$A$1:$J$137</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="511">
   <si>
     <t>类别</t>
   </si>
@@ -1301,6 +1301,9 @@
 或中指小指四缝的瘀络</t>
   </si>
   <si>
+    <t>瘀络</t>
+  </si>
+  <si>
     <t>血一出来，耳朵马上就不痛了。然后补肾。</t>
   </si>
   <si>
@@ -1319,7 +1322,7 @@
     <t>心经</t>
   </si>
   <si>
-    <t>心经上有一条硬结</t>
+    <t>一条硬结</t>
   </si>
   <si>
     <t>把心经上的硬结拔开，也就用了15分钟，黑影没了。</t>
@@ -1353,16 +1356,184 @@
   </si>
   <si>
     <t>吃龙胆泻肝丸。然后隔两天揉一次，揉了不到三个月，好了。
-还可以放血，放大指小指的血，在胆经上找瘀络放血。</t>
-  </si>
-  <si>
-    <t>心主神志</t>
+周说还要放血，放手大指小指的血，在胆经上找瘀络放血，因为心胆别通。</t>
+  </si>
+  <si>
+    <t>精神病</t>
+  </si>
+  <si>
+    <t>或吃蒙石滚痰丸</t>
+  </si>
+  <si>
+    <t>出汗多</t>
+  </si>
+  <si>
+    <t>心阳</t>
+  </si>
+  <si>
+    <t>补阳。补血。</t>
+  </si>
+  <si>
+    <t>不出汗</t>
+  </si>
+  <si>
+    <t>心阴</t>
+  </si>
+  <si>
+    <t>补阴。解表。</t>
+  </si>
+  <si>
+    <t>满脸的褶子</t>
+  </si>
+  <si>
+    <t>心其华在面。揉宗筋。就一次，起来脸上褶子就开了。也可以揉脖子。</t>
+  </si>
+  <si>
+    <t>脸上长斑。满脸全是黑的，就那黄褐斑整个长满了，而且颜色还重</t>
+  </si>
+  <si>
+    <t>心其华在面。我给他揉了三次，揉完三次，脸光光的一个黑点儿都没有。仅治了三次。那会儿我还不会揉脖子，就只揉宗筋。我也是从头这么往下做按摩，但是没有脖子，不会揉脖子，就顺着经络往下走，以宗筋为主。</t>
+  </si>
+  <si>
+    <t>脸上长疙瘩（一脑门子老长疙瘩）</t>
+  </si>
+  <si>
+    <t>心其华在面。</t>
+  </si>
+  <si>
+    <t>鼻头长红疙瘩</t>
+  </si>
+  <si>
+    <t>脾上有热鼻先赤</t>
+  </si>
+  <si>
+    <t>两颐长红疙瘩</t>
+  </si>
+  <si>
+    <t>肾上有热两颐赤</t>
+  </si>
+  <si>
+    <t>右肩关节痛了七八天，疼得晚上不能入睡，手放哪儿都疼</t>
+  </si>
+  <si>
+    <t>右小腿胆经</t>
+  </si>
+  <si>
+    <t>长1厘米的瘀络</t>
+  </si>
+  <si>
+    <t>心胆别通。一针下去，那血就出来，黑血。也就几秒钟，胳膊一动，一点儿都不疼了。</t>
+  </si>
+  <si>
+    <t>浑身胀得难受，左胳膊疼了五年了，左腿也疼麻五年</t>
+  </si>
+  <si>
+    <t>左小腿胆经</t>
+  </si>
+  <si>
+    <t>长1.5厘米的瘀络</t>
+  </si>
+  <si>
+    <t>心胆别通。一针下去，那血跟喷泉似的，他先喷，再流，看着停了稍微一动一使劲儿，它又喷，一共流了40分钟。血一边流，身上的难受一边减轻。这针血下去，整个好，他说比好的这边还轻松，后来在好的这边我又给他放，流的就很少。效果也不那么特别突出。</t>
+  </si>
+  <si>
+    <t>脖子（后项）疼了15年</t>
+  </si>
+  <si>
+    <t>心
+膀胱经</t>
+  </si>
+  <si>
+    <t>小腿胆经膀胱经</t>
+  </si>
+  <si>
+    <t>一大堆瘀络</t>
+  </si>
+  <si>
+    <t>腿上血一放，放完了，脖子一点都不疼了。久病入络，他在络脉上都有明显的表现。
+还是这个病人，第二次脖子疼了又来，给他在大椎穴、胳膊、手都放了血，还疼；又在小腿上放血，放了就不疼了。</t>
+  </si>
+  <si>
+    <t>（右边）三岔神经痛（听宫听会颊车一带）。疼了三天了，又扎针又放血，都没用</t>
+  </si>
+  <si>
+    <t>肾、肝</t>
+  </si>
+  <si>
+    <t>右肾关太溪
+左太冲</t>
+  </si>
+  <si>
+    <t>扎上不到五分钟，不疼了。肾关太溪治的是他的肾火，太冲是去他的肝火。</t>
+  </si>
+  <si>
+    <t>风湿性心脏病，浑身关节疼痛</t>
+  </si>
+  <si>
+    <t>揉脖子，揉了20分钟，好了，不疼了。</t>
+  </si>
+  <si>
+    <t>牛皮癣。痒</t>
+  </si>
+  <si>
+    <t>放血治痒是又快又好。放血的地方要看牛皮癣的位置而定。</t>
+  </si>
+  <si>
+    <t>老年性皮肤瘙痒</t>
+  </si>
+  <si>
+    <t>血虚</t>
+  </si>
+  <si>
+    <t>柏子养心丸、安神补心丸，吃了就好了</t>
+  </si>
+  <si>
+    <t>所有的痒</t>
+  </si>
+  <si>
+    <t>把脖子上的结揉开，给他心脏治好了，他的痒自然就停消了</t>
+  </si>
+  <si>
+    <t>左脸颊长了一个大脓疮，然后吃中药消炎，炎消了之后，不化脓了，留下一个硬疙瘩，又疼又痒</t>
+  </si>
+  <si>
+    <t>周给他捏了两次，回去以后，脓出来了。我说这回你用拔毒膏，记住疮只能用拔毒膏。它这一出脓，就不疼了，这就叫熟了，只要它疼，就是没熟。一定要让这脓出来，如果你不让它出来，憋回去就出大毛病。</t>
+  </si>
+  <si>
+    <t>疮</t>
+  </si>
+  <si>
+    <t>等它自个儿长，自个儿出脓，出脓了，把脓挤干净，或者脓疮上扎几针拔一罐，把脓血放干净。</t>
+  </si>
+  <si>
+    <t>疮在肛周</t>
+  </si>
+  <si>
+    <t>等疮长熟出脓，除了疮上刺络拔罐放血之外，还要在腘窝放血。</t>
+  </si>
+  <si>
+    <t>爱哭</t>
+  </si>
+  <si>
+    <t>心气虚</t>
+  </si>
+  <si>
+    <t>揉脖子</t>
+  </si>
+  <si>
+    <t>碰不得，一碰上就痒</t>
+  </si>
+  <si>
+    <t>心气实</t>
+  </si>
+  <si>
+    <t>右腿胆经</t>
+  </si>
+  <si>
+    <t>心脏淤堵了，心气实则笑不休。放一针血就好。</t>
   </si>
   <si>
     <t>刮痧</t>
-  </si>
-  <si>
-    <t>揉脖子</t>
   </si>
   <si>
     <t>左缺盆压揉酸痛，有一个小米状硬点，还有几个累珠软泡。平时无任何不适</t>
@@ -2379,7 +2550,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25"/>
   <cols>
     <col min="1" max="1" width="7.625" style="1" customWidth="1"/>
@@ -2655,7 +2826,7 @@
       </c>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" ht="40.5" spans="1:10">
+    <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
@@ -3221,7 +3392,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="32" ht="60.75" spans="1:10">
+    <row r="32" ht="40.5" spans="1:10">
       <c r="A32" s="4" t="s">
         <v>10</v>
       </c>
@@ -3249,7 +3420,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="33" ht="60.75" spans="1:10">
+    <row r="33" ht="40.5" spans="1:10">
       <c r="A33" s="4" t="s">
         <v>10</v>
       </c>
@@ -3403,7 +3574,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="39" ht="60.75" spans="1:10">
+    <row r="39" ht="40.5" spans="1:10">
       <c r="A39" s="4" t="s">
         <v>19</v>
       </c>
@@ -4450,7 +4621,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="83" ht="101.25" spans="1:10">
+    <row r="83" ht="81" spans="1:10">
       <c r="A83" s="1" t="s">
         <v>19</v>
       </c>
@@ -4574,7 +4745,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="88" ht="40.5" spans="1:10">
+    <row r="88" spans="1:10">
       <c r="A88" s="1" t="s">
         <v>19</v>
       </c>
@@ -4620,7 +4791,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="90" ht="141.75" spans="1:10">
+    <row r="90" ht="101.25" spans="1:10">
       <c r="A90" s="1" t="s">
         <v>10</v>
       </c>
@@ -4675,7 +4846,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="92" ht="121.5" spans="1:10">
+    <row r="92" ht="101.25" spans="1:10">
       <c r="A92" s="1" t="s">
         <v>19</v>
       </c>
@@ -4698,7 +4869,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="93" ht="121.5" spans="1:10">
+    <row r="93" ht="101.25" spans="1:10">
       <c r="A93" s="1" t="s">
         <v>44</v>
       </c>
@@ -4776,7 +4947,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="96" ht="121.5" spans="1:10">
+    <row r="96" ht="101.25" spans="1:10">
       <c r="A96" s="1" t="s">
         <v>19</v>
       </c>
@@ -4880,7 +5051,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" ht="40.5" spans="1:10">
+    <row r="100" spans="1:10">
       <c r="C100" s="1" t="s">
         <v>356</v>
       </c>
@@ -5055,7 +5226,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="108" ht="60.75" spans="1:10">
+    <row r="108" ht="40.5" spans="1:10">
       <c r="A108" s="1" t="s">
         <v>10</v>
       </c>
@@ -5161,7 +5332,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="113" ht="101.25" spans="1:10">
+    <row r="113" ht="81" spans="1:10">
       <c r="A113" s="1" t="s">
         <v>10</v>
       </c>
@@ -5241,7 +5412,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="117" ht="81" spans="1:10">
+    <row r="117" ht="60.75" spans="1:10">
       <c r="A117" s="1" t="s">
         <v>19</v>
       </c>
@@ -5331,11 +5502,14 @@
       <c r="F121" s="1" t="s">
         <v>418</v>
       </c>
+      <c r="G121" s="1" t="s">
+        <v>419</v>
+      </c>
       <c r="I121" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="122" ht="60.75" spans="1:10">
@@ -5343,13 +5517,19 @@
         <v>10</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>412</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>418</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="123" ht="60.75" spans="1:10">
@@ -5357,7 +5537,7 @@
         <v>10</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>412</v>
@@ -5365,31 +5545,37 @@
       <c r="F123" s="1" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="124" ht="81" spans="1:10">
+      <c r="G123" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" ht="60.75" spans="1:10">
       <c r="A124" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>93</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="125" ht="81" spans="1:10">
@@ -5397,22 +5583,22 @@
         <v>10</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="126" ht="40.5" spans="1:10">
@@ -5420,10 +5606,10 @@
         <v>10</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>41</v>
@@ -5435,7 +5621,7 @@
         <v>93</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="127" ht="40.5" spans="1:10">
@@ -5443,42 +5629,384 @@
         <v>10</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="128" ht="81" spans="1:10">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="128" ht="101.25" spans="1:10">
       <c r="A128" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>93</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="129" spans="3:3">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="129" spans="3:10">
       <c r="C129" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="130" spans="3:10">
+      <c r="C130" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="J130" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="131" spans="3:10">
+      <c r="C131" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="132" ht="60.75" spans="3:10">
+      <c r="C132" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="133" ht="141.75" spans="3:10">
+      <c r="C133" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="134" ht="40.5" spans="3:10">
+      <c r="C134" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="135" spans="3:10">
+      <c r="C135" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="136" spans="3:10">
+      <c r="C136" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J136" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="137" ht="60.75" spans="3:10">
+      <c r="C137" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J137" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="138" ht="162" spans="3:10">
+      <c r="C138" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="139" ht="141.75" spans="3:10">
+      <c r="C139" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J139" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="140" ht="81" spans="3:10">
+      <c r="C140" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="141" ht="40.5" spans="3:10">
+      <c r="C141" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="142" ht="40.5" spans="3:10">
+      <c r="C142" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="143" ht="40.5" spans="3:10">
+      <c r="C143" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="144" ht="40.5" spans="3:10">
+      <c r="C144" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="145" ht="141.75" spans="3:10">
+      <c r="C145" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="146" ht="60.75" spans="3:10">
+      <c r="C146" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="147" ht="40.5" spans="3:10">
+      <c r="C147" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="148" spans="3:10">
+      <c r="C148" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="149" spans="3:10">
+      <c r="C149" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J149" s="1" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="150" ht="40.5" spans="3:10">
+      <c r="C150" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J150" s="1" t="s">
+        <v>494</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J129" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J137" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5502,15 +6030,15 @@
         <v>93</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>438</v>
+        <v>495</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>439</v>
+        <v>490</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>440</v>
+        <v>496</v>
       </c>
       <c r="C2" s="2">
         <v>4</v>
@@ -5518,10 +6046,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>441</v>
+        <v>497</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>442</v>
+        <v>498</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -5535,7 +6063,7 @@
         <v>140</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>443</v>
+        <v>499</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -5543,7 +6071,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>444</v>
+        <v>500</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
@@ -5551,7 +6079,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>445</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -5574,29 +6102,29 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="B1" s="1" t="s">
-        <v>446</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>439</v>
+        <v>490</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>447</v>
+        <v>503</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>448</v>
+        <v>504</v>
       </c>
     </row>
     <row r="3" ht="141.75" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>449</v>
+        <v>505</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>450</v>
+        <v>506</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>451</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5604,10 +6132,10 @@
         <v>381</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>450</v>
+        <v>506</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>452</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5615,10 +6143,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>453</v>
+        <v>509</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>454</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>

--- a/docs/addendum_AI_list.xlsx
+++ b/docs/addendum_AI_list.xlsx
@@ -12,7 +12,7 @@
     <sheet name="核心奥义" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AI清单!$A$1:$J$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AI清单!$A$1:$J$268</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="799">
   <si>
     <t>类别</t>
   </si>
@@ -175,30 +175,33 @@
     <t>坐骨神经痛</t>
   </si>
   <si>
+    <t>屁股痛。扎针、拔罐、按摩屁股，治了七八天，还是痛</t>
+  </si>
+  <si>
+    <t>屁股</t>
+  </si>
+  <si>
+    <t>同侧肩中带</t>
+  </si>
+  <si>
+    <t>重按轻提</t>
+  </si>
+  <si>
+    <t>手臂痛</t>
+  </si>
+  <si>
     <t>痛</t>
   </si>
   <si>
-    <t>屁股</t>
-  </si>
-  <si>
-    <t>同侧肩中带</t>
+    <t>手臂</t>
+  </si>
+  <si>
+    <t>云门</t>
   </si>
   <si>
     <t>重点轻提</t>
   </si>
   <si>
-    <t>扎针、拔罐、按摩屁股，治了七八天，还是痛</t>
-  </si>
-  <si>
-    <t>手臂痛</t>
-  </si>
-  <si>
-    <t>手臂</t>
-  </si>
-  <si>
-    <t>云门</t>
-  </si>
-  <si>
     <t>胸闷、胸痛、气短、头晕</t>
   </si>
   <si>
@@ -214,7 +217,7 @@
     <t>把黑云揉散</t>
   </si>
   <si>
-    <t>卒死</t>
+    <t>突然昏迷</t>
   </si>
   <si>
     <t>至阳</t>
@@ -223,7 +226,7 @@
     <t>按揉</t>
   </si>
   <si>
-    <t>力度、层次要达到</t>
+    <t>揉了几分钟，人缓过来了。如果力度、层次达到的话，一分钟就能缓过来</t>
   </si>
   <si>
     <t>腰痛</t>
@@ -1482,7 +1485,7 @@
     <t>老年性皮肤瘙痒</t>
   </si>
   <si>
-    <t>血虚</t>
+    <t>心血虚</t>
   </si>
   <si>
     <t>柏子养心丸、安神补心丸，吃了就好了</t>
@@ -1533,6 +1536,882 @@
     <t>心脏淤堵了，心气实则笑不休。放一针血就好。</t>
   </si>
   <si>
+    <t>眼白红一块</t>
+  </si>
+  <si>
+    <t>黄连羊肝丸，吃了就会好</t>
+  </si>
+  <si>
+    <t>一揉宗筋就好了</t>
+  </si>
+  <si>
+    <t>眼白红了20年，且眼睛不舒服，他往里抽，很难受的</t>
+  </si>
+  <si>
+    <t>揉宗筋揉了十分钟，立刻好了。</t>
+  </si>
+  <si>
+    <t>眼睛干涩，看十分钟电脑，立刻就得躺下闭眼休息</t>
+  </si>
+  <si>
+    <t>石斛夜光丸。一般刚开始眼睛干涩，吃上一礼拜保证就好</t>
+  </si>
+  <si>
+    <t>眼睛干涩见风流泪，一早上起来这俩眼（左眼更严重）哗哗地流泪</t>
+  </si>
+  <si>
+    <t>揉脖子眼点（右颊车颌骨下沿），就揉了20分钟，好了，立刻眼泪就没了</t>
+  </si>
+  <si>
+    <t>眼白红、口苦、尿黄</t>
+  </si>
+  <si>
+    <t>龙胆泻肝丸</t>
+  </si>
+  <si>
+    <t>视神经炎，视神经萎缩，视网膜炎</t>
+  </si>
+  <si>
+    <t>石斛夜光丸，最少吃上一年，因为小孩嘛。好了，视网膜炎也好了。到现在三年了，一点事没有。</t>
+  </si>
+  <si>
+    <t>眼睛干涩，睁不开。吃一专家开的药吃了50副药之后，不但眼睛睁不开，嘴也张不开了。说明治反了</t>
+  </si>
+  <si>
+    <t>揉了十多分钟的脖子，眼睛睁开了。回去吃石斛夜光丸</t>
+  </si>
+  <si>
+    <t>一个眼珠子疼</t>
+  </si>
+  <si>
+    <t>龙胆泻肝丸。吃两天就能好。</t>
+  </si>
+  <si>
+    <t>灰指甲</t>
+  </si>
+  <si>
+    <t>就揉宗筋就揉好了</t>
+  </si>
+  <si>
+    <t>一初中生，一看书头就晕，他的指甲跟那个软蛋壳似的，高压160，低压100，血压高</t>
+  </si>
+  <si>
+    <t>揉了几回就好了，小孩好得快</t>
+  </si>
+  <si>
+    <t>满后背疼，但又说不清楚究竟是哪疼</t>
+  </si>
+  <si>
+    <t>吃点平肝舒络丸就好了。或者揉宗筋，一揉就好了。</t>
+  </si>
+  <si>
+    <t>一摇脖子嘎嘎作响，或者肩响，或者膝盖响，脚腕子响，手腕子响，嘎嘣嘎嘣响，因为肝坏了，筋变硬了，牵拉得太厉害，你一动弹之后，骨跟骨之间摩擦就响</t>
+  </si>
+  <si>
+    <t>揉揉宗筋就好了</t>
+  </si>
+  <si>
+    <t>站五分钟就得躺下，他站不住。</t>
+  </si>
+  <si>
+    <t>揉宗筋，揉了五六次之后，他就可以站一个多小时了。治了半年多，他就出去旅游去了。</t>
+  </si>
+  <si>
+    <t>当你肝不好之后，你抽筋儿可厉害了，连肚子都抽筋儿，肚子抽筋儿比腿抽筋儿还难受</t>
+  </si>
+  <si>
+    <t>疏肝，然后补肾，把肝疏了一定要补肾。</t>
+  </si>
+  <si>
+    <t>血压高，高压180，低压120</t>
+  </si>
+  <si>
+    <t>降压四步</t>
+  </si>
+  <si>
+    <t>治15分钟，再量血压，不高了，正常了，90， 140。</t>
+  </si>
+  <si>
+    <t>血压高，高压180，低压120。高压高是肝瘀，低压高是肾虚</t>
+  </si>
+  <si>
+    <t>眩晕</t>
+  </si>
+  <si>
+    <t>用了半年的时间，把血压高治好了。我基本上没吃降压药，偶尔的吃个一粒两粒的，因为太难受的时候才吃。</t>
+  </si>
+  <si>
+    <t>一，拽耳尖。一手提对侧耳尖往上拽。
+二，揉大椎两侧。把大椎穴两侧的结揉开。
+三，推肚子。攥着拳头，肋骨以下就是软和的，从软和的往下推，一直推到腹股沟，使劲地推，你会推到肚子里头有硬结，把那结推开。推右边降高压，推左边降低压。
+四，如果是高压高，扎一针太冲穴就管用；如果是低压高，是肾气不足，揉小腿肚，小腿肚上会有很硬的结，按起来很痛，给他摁到不痛。拿胳膊肘子肘，用手指头揉不开。</t>
+  </si>
+  <si>
+    <t>左肩膀不舒服</t>
+  </si>
+  <si>
+    <t>左腋</t>
+  </si>
+  <si>
+    <t>有结，按着很痛</t>
+  </si>
+  <si>
+    <t>月经不正常</t>
+  </si>
+  <si>
+    <t>腋</t>
+  </si>
+  <si>
+    <t>腋下有结，按着很痛</t>
+  </si>
+  <si>
+    <t>把结揉开，月经就正常了</t>
+  </si>
+  <si>
+    <t>右腋下嘟出去一大块，就是附乳</t>
+  </si>
+  <si>
+    <t>心情不好，小心眼儿</t>
+  </si>
+  <si>
+    <t>捋</t>
+  </si>
+  <si>
+    <t>一边72下，每天捋</t>
+  </si>
+  <si>
+    <t>腰疼、颈椎疼，眼睛还干涩</t>
+  </si>
+  <si>
+    <t>风</t>
+  </si>
+  <si>
+    <t>偏头痛</t>
+  </si>
+  <si>
+    <t>胆经</t>
+  </si>
+  <si>
+    <t>足临泣穴</t>
+  </si>
+  <si>
+    <t>扎</t>
+  </si>
+  <si>
+    <t>四五年的偏头痛，一针扎完就好了</t>
+  </si>
+  <si>
+    <t>脑血栓，又叫脑中风</t>
+  </si>
+  <si>
+    <t>肝经胆经</t>
+  </si>
+  <si>
+    <t>嘴歪眼斜，又叫面瘫、面部中风、面部神经麻痹</t>
+  </si>
+  <si>
+    <t>胆经
+大肠经</t>
+  </si>
+  <si>
+    <t>风池合谷太冲</t>
+  </si>
+  <si>
+    <t>风三针，治面瘫，一治就好</t>
+  </si>
+  <si>
+    <t>痛风，痛在大脚趾肝经上</t>
+  </si>
+  <si>
+    <t>肝经</t>
+  </si>
+  <si>
+    <t>风市</t>
+  </si>
+  <si>
+    <t>或扎水火即济+肝震位，扎上15分钟准好</t>
+  </si>
+  <si>
+    <t>痛风，痛在大脚趾脾经上</t>
+  </si>
+  <si>
+    <t>风市+脾经火穴</t>
+  </si>
+  <si>
+    <t>或扎水火即济+脾坤位</t>
+  </si>
+  <si>
+    <t>痛风，痛在小脚趾胆经上</t>
+  </si>
+  <si>
+    <t>或扎水火即济+胆巽位</t>
+  </si>
+  <si>
+    <t>痛风，痛在手大姆指上</t>
+  </si>
+  <si>
+    <t>肺经</t>
+  </si>
+  <si>
+    <t>风市+肺经火穴？肺经母穴</t>
+  </si>
+  <si>
+    <t>或扎水火即济+肺兑位</t>
+  </si>
+  <si>
+    <t>脚后跟痛</t>
+  </si>
+  <si>
+    <t>风府</t>
+  </si>
+  <si>
+    <t>有一个硬结</t>
+  </si>
+  <si>
+    <t>把硬结揉开，揉到不痛，就好了</t>
+  </si>
+  <si>
+    <t>掉</t>
+  </si>
+  <si>
+    <t>19岁，就这么抽，抽了十年，而且抽着抽着会突然“嗷”地叫一声，他叫了就舒服很多</t>
+  </si>
+  <si>
+    <t>揉宗筋揉了两回就好了，孩子好得快。但过两天又犯了，因为他妈又气他，另外他家风水不对，他的床又在巽位，所以得肝病</t>
+  </si>
+  <si>
+    <t>从一岁开始左右半身不遂，也抽，但抽得没前一个厉害，而且说话语速快，没人听得懂</t>
+  </si>
+  <si>
+    <t>揉了两回，语速慢下来了，说话能听懂了。后来调了风水阴宅，左右半身不遂治好了80%</t>
+  </si>
+  <si>
+    <t>不停地哆嗦，夜里睡觉也不停，哆嗦了四年。到处看，看了四年没人治得好，也查不出是啥病</t>
+  </si>
+  <si>
+    <t>揉宗筋揉了三次，第四次再来，不哆嗦了。</t>
+  </si>
+  <si>
+    <t>帕金森综合症</t>
+  </si>
+  <si>
+    <t>四大核心运动症状：颤抖晃动、动作或表情迟缓、肌肉强直、平衡不稳</t>
+  </si>
+  <si>
+    <t>这是肝瘀肾亏的极致表现，用药有矛盾，只有用按摩的手法是最好的。照样可以治好，一点问题没有。</t>
+  </si>
+  <si>
+    <t>眩</t>
+  </si>
+  <si>
+    <t>晕，晕得不行了，头不动都晕。还吃不下饭，胸口这堵一大疙瘩。还糖尿病，右胳膊抬不起来，右腿疼，这都是糖尿病的表现</t>
+  </si>
+  <si>
+    <t>揉了三次，能吃饭了；揉四次，不晕了，就是在扭头的某一个位置上还犯晕，这是颈椎病；揉十次，胳膊也好了，腿也好了，扭头任何位置都不晕了。</t>
+  </si>
+  <si>
+    <t>晕了一年多，晕者虚，他虚得都不行了</t>
+  </si>
+  <si>
+    <t>揉了几次，好了。过一段时间又犯又来，师问饮食，原来他们一家三口一个月吃十斤油，油由胆汁消化，怪不得生肝病。少吃油，再治，彻底的好了。</t>
+  </si>
+  <si>
+    <t>一个小孩九岁，乳头疼</t>
+  </si>
+  <si>
+    <t>一扎就好了</t>
+  </si>
+  <si>
+    <t>不孕症</t>
+  </si>
+  <si>
+    <t>揉了七次，怀上女儿了；揉上三个月，应该可以怀上儿子（师未直言）</t>
+  </si>
+  <si>
+    <t>闭经</t>
+  </si>
+  <si>
+    <t>闭经。肝气瘀结闭经，很多不来月经的、月经特别少的、颜色特别重的</t>
+  </si>
+  <si>
+    <t>宗筋一揉就好。轻的吃点加味逍遥丸。</t>
+  </si>
+  <si>
+    <t>闭经。寒凉引起的闭经，轻的是痛经，重的就闭经</t>
+  </si>
+  <si>
+    <t>陶道
+八髎长强</t>
+  </si>
+  <si>
+    <t>一是搓八髎点长强。
+二是灸陶道2个小时。</t>
+  </si>
+  <si>
+    <t>闭经。肾虚引起的闭经。基本没来过月经，18岁时靠打激素来过半年月经，但这半年浑身哪哪都难受，他再不愿打激素了</t>
+  </si>
+  <si>
+    <t>金匮肾气丸。吃了一年，月经正常了，胳膊也不疼了，腰也不疼了，哪儿都好了，那什么什么尺神经炎也好了（下关骨痛，一开始是嚼东西痛，后来张嘴都痛，最后都张不开嘴了，张开一点就痛）。又继续吃了8个月，上火了，牙全肿了，停金匮，吃六味。</t>
+  </si>
+  <si>
+    <t>闭经。脾胃引起的闭经</t>
+  </si>
+  <si>
+    <t>治他的脾胃，治一段时间，好了，脾胃很难调的。</t>
+  </si>
+  <si>
+    <t>阳痿</t>
+  </si>
+  <si>
+    <t>由于心脏引起的阳痿</t>
+  </si>
+  <si>
+    <t>龟头扎一针放血</t>
+  </si>
+  <si>
+    <t>由于脾胃引起阳痿，特征是连想法都没了，因为脾主意。</t>
+  </si>
+  <si>
+    <t>由于肝脏引起的阳痿，特征是肝气瘀结了</t>
+  </si>
+  <si>
+    <t>由于肾亏引起的阳痿</t>
+  </si>
+  <si>
+    <t>胆儿小害怕</t>
+  </si>
+  <si>
+    <t>肝气虚</t>
+  </si>
+  <si>
+    <t>补肾</t>
+  </si>
+  <si>
+    <t>爱生气发怒</t>
+  </si>
+  <si>
+    <t>肝气实</t>
+  </si>
+  <si>
+    <t>揉宗筋揉五次，就生不起气了</t>
+  </si>
+  <si>
+    <t>脑肿瘤</t>
+  </si>
+  <si>
+    <t>脑肿瘤，压迫视神经了，看不清东西</t>
+  </si>
+  <si>
+    <t>有明显的瘀络</t>
+  </si>
+  <si>
+    <t>放了600CC。好几次医者都想给止住，患者说，别止，让他留，我已经能看清东西了。你看看他，随着他放血，他的肿瘤就在减小。这一针血下来，起码好了60%</t>
+  </si>
+  <si>
+    <t>脑子里边瘀堵了、梗塞了</t>
+  </si>
+  <si>
+    <t>脑子里边不管长什么东西，你都在腘窝处放血。</t>
+  </si>
+  <si>
+    <t>脑鸣</t>
+  </si>
+  <si>
+    <t>大脚趾</t>
+  </si>
+  <si>
+    <t>撞车之后半身不遂，这胳膊也直不了，这腿也走不了了</t>
+  </si>
+  <si>
+    <t>捏着很疼</t>
+  </si>
+  <si>
+    <t>上午一个半小时，下午一个半小时，就捏大脚趾。捏三天，好了</t>
+  </si>
+  <si>
+    <t>半身不遂之后，胳膊腿动唤不了了</t>
+  </si>
+  <si>
+    <t>捏了七天也好了</t>
+  </si>
+  <si>
+    <t>半身不遂，说不出话来</t>
+  </si>
+  <si>
+    <t>肚脐附近里面有结</t>
+  </si>
+  <si>
+    <t>推</t>
+  </si>
+  <si>
+    <t>在肚子上胡噜不到5分钟，把那个结往下一拉，拉完之后，话说出来了</t>
+  </si>
+  <si>
+    <t>脑瘤，十三四岁一个小孩</t>
+  </si>
+  <si>
+    <t>肚脐下面的动气歪了</t>
+  </si>
+  <si>
+    <t>用了17次，把脑瘤给治没了</t>
+  </si>
+  <si>
+    <t>左侧半身不遂，胳膊动不了，说话也困难</t>
+  </si>
+  <si>
+    <t>围着肚脐一圈硬的大圆盘</t>
+  </si>
+  <si>
+    <t>扎针
+揉</t>
+  </si>
+  <si>
+    <t>慢慢地揉软和了就好了</t>
+  </si>
+  <si>
+    <t>白天晚上不分，不认识路，不清醒</t>
+  </si>
+  <si>
+    <t>大椎
+宗筋</t>
+  </si>
+  <si>
+    <t>大椎有一个结</t>
+  </si>
+  <si>
+    <t>把大椎两侧的结揉开，病轻的马上就能清醒。
+再加上揉宗筋，严重的也只用了三次，就整明白了，第四次就是自己坐公交车来的了。揉了十几次，效果非常好。
+同时吃六味地黄丸。</t>
+  </si>
+  <si>
+    <t>脑病关键在于补肾</t>
+  </si>
+  <si>
+    <t>骨</t>
+  </si>
+  <si>
+    <t>牙齿暴长，又痒又痛又难受。</t>
+  </si>
+  <si>
+    <t>白术熬水漱口，一治就好了。</t>
+  </si>
+  <si>
+    <t>脚上长骨刺</t>
+  </si>
+  <si>
+    <t>白术熬水泡脚。</t>
+  </si>
+  <si>
+    <t>年老耳背眼花</t>
+  </si>
+  <si>
+    <t>天天补肾，不能间断</t>
+  </si>
+  <si>
+    <t>六七岁的小男孩，耳背，他的听力只是常人的三分之一</t>
+  </si>
+  <si>
+    <t>睾丸</t>
+  </si>
+  <si>
+    <t>他的睾丸只有常人的三分之一大，正常约两厘米大</t>
+  </si>
+  <si>
+    <t>捏睾丸，天天捏，捏了三个半月，把睾丸捏到正常大小了，他耳背就好了。</t>
+  </si>
+  <si>
+    <t>每天下午六点钟吃6颗黑豆</t>
+  </si>
+  <si>
+    <t>憋不住尿，一咳嗽就漏尿</t>
+  </si>
+  <si>
+    <t>金匮肾气丸</t>
+  </si>
+  <si>
+    <t>尿频尿急尿不尽</t>
+  </si>
+  <si>
+    <t>便秘。肾阳虚引起的便秘，特征是肚子不会痛，常拌随腿痛（膀胱经）</t>
+  </si>
+  <si>
+    <t>金匮肾气丸。吃了一个星期就好了</t>
+  </si>
+  <si>
+    <t>便秘。肠胃火引起的便秘，特征是肚子痛，常伴善饥、口臭</t>
+  </si>
+  <si>
+    <t>麻仁润肠丸</t>
+  </si>
+  <si>
+    <t>便秘。肝火引起的便秘，特征是肚子痛，常伴易怒、口苦</t>
+  </si>
+  <si>
+    <t>龙胆泻肝丸。平常可以喝点茵陈蒿汤
+一揉宗筋它就会好了</t>
+  </si>
+  <si>
+    <t>脱肛</t>
+  </si>
+  <si>
+    <t>足底肛点</t>
+  </si>
+  <si>
+    <t>一摁剧痛</t>
+  </si>
+  <si>
+    <t>在那剧痛的肛点，玩命的摁，摁了一阵，那肛门刷刷收回去了。然后吃金匮肾气丸。</t>
+  </si>
+  <si>
+    <t>子宫脱垂</t>
+  </si>
+  <si>
+    <t>金匮肾气丸。很严重的子宫脱垂，吃了半年的金匮肾气丸，好了。</t>
+  </si>
+  <si>
+    <t>吃东西老呛，得慢慢地吃，严重的慢慢吃都不行，喝水它都能喷呛</t>
+  </si>
+  <si>
+    <t>肾关太溪</t>
+  </si>
+  <si>
+    <t>扎完就好了，再也不呛了</t>
+  </si>
+  <si>
+    <t>其它地方都瘦了，就胃这儿鼓，非常鼓</t>
+  </si>
+  <si>
+    <t>梅花针敲，敲完拔罐放血，血一出来，肚子扑哧瘪了</t>
+  </si>
+  <si>
+    <t>胃里胀气，气都胀到整个上半身了，手臂也被气架着放不下来，感觉很难受</t>
+  </si>
+  <si>
+    <t>先扎了两针，没怎么管用。再用梅花针敲了四五十下，给他疼的。敲完之后一拔罐。这血一出来，他说就像这肚子里的东西扑嚓一下掉下去了，跟那生孩子似的，一下子这肚子里就空了。</t>
+  </si>
+  <si>
+    <t>心慌，心跟悬着似的，很难受，还老饿。按冠心病治了12年，没治好</t>
+  </si>
+  <si>
+    <t>太溪</t>
+  </si>
+  <si>
+    <t>扎了一针，当时就好了</t>
+  </si>
+  <si>
+    <t>老饿，越到晚上越饿，使劲的吃</t>
+  </si>
+  <si>
+    <t>扎了一针，好了</t>
+  </si>
+  <si>
+    <t>尿血，尿了三年的血</t>
+  </si>
+  <si>
+    <t>肾寒</t>
+  </si>
+  <si>
+    <t>金匮肾气丸，然后白茅根熬水喝。一治，他就不尿血了，立刻就好了</t>
+  </si>
+  <si>
+    <t>17岁，浑身疼，发高烧，老是39度、40度。在西医住了一个星期烧退不了，就给转到中医科，中医科治了一个星期烧还退不了。诊断为强直性脊柱炎</t>
+  </si>
+  <si>
+    <t>附子100g，吃完了那烧就开始退。吃了一个礼拜，又加了一味药灸甘草，药方变成附子100g，灸甘草50g，又吃一个礼拜烧全退了。不但烧退了，疼痛减轻了多一半。</t>
+  </si>
+  <si>
+    <t>小孩子发烧</t>
+  </si>
+  <si>
+    <t>身柱</t>
+  </si>
+  <si>
+    <t>艾灸身柱穴。助阳。阳气助起来，把阴就给压下去，烧就自然退了。这才是正确的退烧方式。</t>
+  </si>
+  <si>
+    <t>睾丸炎，痛，肿，牵着小肚子里边都痛，非常难受。到医院消炎，打吊针，打完之后一宿没睡觉，因为更疼了。治反了，不能消炎，不能寒凉。</t>
+  </si>
+  <si>
+    <t>艾灸身柱穴。必须灸他2个小时，灸完之后，它一直热能串到睾丸上去。灸一次，当时就不疼了。</t>
+  </si>
+  <si>
+    <t>男性二阴及生殖方面的寒凉</t>
+  </si>
+  <si>
+    <t>女性二阴及生殖方面的寒凉</t>
+  </si>
+  <si>
+    <t>陶道</t>
+  </si>
+  <si>
+    <t>30年的痛经，子宫内膜异位、子宫禁忌症，她的子宫壁厚得简直都不行了，所以他每次来例假都疼得死去活来，而且还发烧，非常之难受。</t>
+  </si>
+  <si>
+    <t>一次灸3个小时。我给他灸了三次，他再来例假，好了。</t>
+  </si>
+  <si>
+    <t>子宫内膜禁忌症，扎脐针扎了半年，没好。没好还没关系，这人已经上一层楼都上不动了，整个给扎虚死了。</t>
+  </si>
+  <si>
+    <t>肾寒加虚</t>
+  </si>
+  <si>
+    <t>我给他揉三次，每次20分钟，他没那么大气力，没有气血调动，所以不能揉时间长了。三次之后，上楼不喘了，不那么虚了。他被扎虚了，得先补，得用补法，然后再说去寒。可不是一疏通他就好，没那么简单。</t>
+  </si>
+  <si>
+    <t>桂附地黄丸或者金匮肾气丸，或者左归丸</t>
+  </si>
+  <si>
+    <t>四川的一个病人，腿肿，按摩治了，好一点，可他回去吃盐一多了他就还肿。</t>
+  </si>
+  <si>
+    <t>吃三个月的白食，三个月里不许吃盐</t>
+  </si>
+  <si>
+    <t>一个学生，浑身都瘫了似的，根本就站不起来，走不了路。怎么得的？踢足球踢热了，踢完了之后往地下一坐，地上凉，就那么坐了不到1小时，这人就起不来了。治了两年了，到处治治不好。</t>
+  </si>
+  <si>
+    <t>治脑三法</t>
+  </si>
+  <si>
+    <t>头痛了30年，到处治治不好。怎么得的？就跟那强力举重似的，干活努住了</t>
+  </si>
+  <si>
+    <t>扎一针就好</t>
+  </si>
+  <si>
+    <t>小伙子，头疼。怎么得的？在部队里头，参加比赛，提着两桶水，看谁走得快，走得最快，走完了，头疼了，这就叫强力举重。</t>
+  </si>
+  <si>
+    <t>膝关节痛</t>
+  </si>
+  <si>
+    <t>膝关节痛，上楼下楼痛。</t>
+  </si>
+  <si>
+    <t>先补肾，阳虚补阳，阴虚补阴。再揉白环俞，一揉就好。</t>
+  </si>
+  <si>
+    <t>膝关节痛，嘎嘎作响。</t>
+  </si>
+  <si>
+    <t>膝关节痛，伴随有其它的心脏病表现，如胸盈胸闷。</t>
+  </si>
+  <si>
+    <t>一揉脖子就好了</t>
+  </si>
+  <si>
+    <t>膝关节痛，且肿。</t>
+  </si>
+  <si>
+    <t>揉两次，那肿就能下去</t>
+  </si>
+  <si>
+    <t>膝关节痛，别的关节也痛。</t>
+  </si>
+  <si>
+    <t>大肠俞、天枢</t>
+  </si>
+  <si>
+    <t>这是治肺引起的关节疼痛的两大要点。</t>
+  </si>
+  <si>
+    <t>六十多岁老太太，每天都要难受，非常难受，越到下午越难受</t>
+  </si>
+  <si>
+    <t>肾阴虚</t>
+  </si>
+  <si>
+    <t>肾阴虚则厥。揉了两次，今天揉前面，明天揉后面，然后回家吃六味地黄丸，好了，到现在一年多了，老太太欢蹦乱跳的，老爱跳舞了，什么都挺好。</t>
+  </si>
+  <si>
+    <t>八十多老太太，骨头热，叫骨蒸，特别难受，卧床不起有十来天了。大夫说您回去准备装椁衣服。</t>
+  </si>
+  <si>
+    <t>六味地黄丸。一次两丸，一天三次。吃三天，下地了。吃一个礼拜，好好的。六味地黄丸救条命。</t>
+  </si>
+  <si>
+    <t>女，50多岁，呼呼的出汗</t>
+  </si>
+  <si>
+    <t>周给他按摩了十多次，居然治不好，没辙了，拔肛门。肛门里跟空洞似的。空也摁。拔完一次好了60%，三次彻底好。</t>
+  </si>
+  <si>
+    <t>男子补肾</t>
+  </si>
+  <si>
+    <t>捏睾丸</t>
+  </si>
+  <si>
+    <t>女子补肾</t>
+  </si>
+  <si>
+    <t>拔肛门</t>
+  </si>
+  <si>
+    <t>乙肝病人，周给他治得指标都正常了，就是转氨酶还高。</t>
+  </si>
+  <si>
+    <t>拔一次，转氨酶就正常了</t>
+  </si>
+  <si>
+    <t>糖尿病指标高</t>
+  </si>
+  <si>
+    <t>拔一次，指标就正常了</t>
+  </si>
+  <si>
+    <t>哮喘，12年，6年西医没治好，6年中药没治好。有痰</t>
+  </si>
+  <si>
+    <t>补脾益肠丸+六味地黄丸，40天，结合10次按摩，全好。</t>
+  </si>
+  <si>
+    <t>哮喘，40年，惊恐致喘，无痰干喘</t>
+  </si>
+  <si>
+    <t>涌泉</t>
+  </si>
+  <si>
+    <t>有结</t>
+  </si>
+  <si>
+    <t>治肾，治了七八次，就给他整好了。</t>
+  </si>
+  <si>
+    <t>生气加惊吓引起的哮喘，无痰干喘</t>
+  </si>
+  <si>
+    <t>足底涌泉、肝区</t>
+  </si>
+  <si>
+    <t>拔肛门，补肾；揉宗筋，舒肝。</t>
+  </si>
+  <si>
+    <t>哮喘</t>
+  </si>
+  <si>
+    <t>不想吃饭，胃口不好</t>
+  </si>
+  <si>
+    <t>肘肺经</t>
+  </si>
+  <si>
+    <t>实则泻其子。血一出来，几分钟，就饿了。</t>
+  </si>
+  <si>
+    <t>心绞痛</t>
+  </si>
+  <si>
+    <t>二脚趾</t>
+  </si>
+  <si>
+    <t>在第二脚趾的下边（掌侧根节），扎几针放血，血一出来马上心绞痛就去掉了。实则泻其子</t>
+  </si>
+  <si>
+    <t>揉脖子泻心。实则泻其子</t>
+  </si>
+  <si>
+    <t>肾炎，不是很严重的话</t>
+  </si>
+  <si>
+    <t>喝白茅根水喝上一段时间它就好了。虚则补其母</t>
+  </si>
+  <si>
+    <t>心慌心悸，手脚冰凉，非常难受</t>
+  </si>
+  <si>
+    <t>急治法。扎脐针水火即济。山泽通气必须先扎山，后治泽；水火既济必须先治水，因为它就是肾的问题，你不能先治火，你治火他就更兴奋了。必须先治水。一扎上坎位，他就好多了，还没扎离位呢，他就好多了，完了再一针，水火即济，马上好，一分钟之内立刻好。</t>
+  </si>
+  <si>
+    <t>根治法。脐针扎完歇一会儿，再按摩。捏睾丸。捏睾丸的时候，他说一下子就窜到腰，他说我就这儿老腰疼，就窜到腰疼的那个位置。捏睾丸很疼，越疼越捏，然后捏到他不疼了，他一下子就松开了，一下子腰也不疼了，整个人都舒服了。捏通了以后你再捏它就不疼了。就是捏睾丸。治的是肾。从那次以后，到现在七八年了，他再也不心慌了。然后回去就补肾，补肾阴，六味地黄丸。</t>
+  </si>
+  <si>
+    <t>心跳过缓</t>
+  </si>
+  <si>
+    <t>补肾阳。金匮肾气丸、桂附地黄丸或者右归丸都可以，吃上一段时间，心跳就正常了</t>
+  </si>
+  <si>
+    <t>心跳过快</t>
+  </si>
+  <si>
+    <t>补肾阴。六味地黄丸、左归丸。</t>
+  </si>
+  <si>
+    <t>乳腺增生、乳房结节、乳腺囊肿、乳腺肿瘤</t>
+  </si>
+  <si>
+    <t>昆仑</t>
+  </si>
+  <si>
+    <t>内有结节，外表看着是鼓的，有压痛</t>
+  </si>
+  <si>
+    <t>扎同侧昆仑。先扎昆仑上一寸，停一会儿，让气往下走一走，然后再扎第二针，昆仑。扎完昆仑再停一停，然后再扎第三针，昆仑下（半寸）。这是三针昆仑穴，治乳腺增生，立刻就好</t>
+  </si>
+  <si>
+    <t>右侧乳房（鹰窗与天泉之间）撞了一下，撞出如核桃大一硬疙瘩，很痛。</t>
+  </si>
+  <si>
+    <t>扎同侧昆仑。就扎了一针，扎完之后，他那个结立刻就化了。当时就化，马上就好</t>
+  </si>
+  <si>
+    <t>肾寒凉</t>
+  </si>
+  <si>
+    <t>揉脖子治心，用心的火去袪肾的寒</t>
+  </si>
+  <si>
+    <t>腿寒凉</t>
+  </si>
+  <si>
+    <t>放手小指的血</t>
+  </si>
+  <si>
+    <t>口臭20年，奇臭</t>
+  </si>
+  <si>
+    <t>表现为胃的病，实际是木克土，是生气生的，肝气郁结，伤及脾胃。这是肝火，所以治木。龙胆泻肝丸。吃了三天好了80%，一个礼拜全好，一点口臭都没有了。</t>
+  </si>
+  <si>
+    <t>老打嗝，一碰就打</t>
+  </si>
+  <si>
+    <t>也是木克土，吃点疏肝丸就好了。</t>
+  </si>
+  <si>
+    <t>两肋串痛，治了八个月，治不好</t>
+  </si>
+  <si>
+    <t>脾胃</t>
+  </si>
+  <si>
+    <t>疏肝丸。或者揉宗筋，揉两三次就好了。这也是木克土的典型案例，表面是脾胃的病，实则是肝瘀。</t>
+  </si>
+  <si>
+    <t>脂肪瘤，长在肉里边的疙瘩</t>
+  </si>
+  <si>
+    <t>木克土克过了，造成土地板结。因为肝瘀了。舒肝丸。</t>
+  </si>
+  <si>
+    <t>皮肤表面长出小肉瘤小肉疙瘩</t>
+  </si>
+  <si>
+    <t>木不克土，造成土地流失。因为肝阳不足以固土。脐针扎巽位。就扎了三次，他满胸脯的小肉瘤就都下去了，没了。
+也可以扎胆经土穴。</t>
+  </si>
+  <si>
+    <t>将近300斤一米八几的大胖子，他找我治血压高，他血压高吃降压药都没用了</t>
+  </si>
+  <si>
+    <t>我给他揉了五次，血压正常了。他说周大夫你还把我一个病治好了，大脚趾痛风，以前动不得，已经六年了，揉五次好了。同时体重减了10公斤，饭量增了三倍。</t>
+  </si>
+  <si>
+    <t>火克金</t>
+  </si>
+  <si>
     <t>刮痧</t>
   </si>
   <si>
@@ -1549,9 +2428,6 @@
   </si>
   <si>
     <t>综合</t>
-  </si>
-  <si>
-    <t>胆经</t>
   </si>
   <si>
     <t>核心奥义</t>
@@ -2550,7 +3426,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J150"/>
+  <dimension ref="A1:K274"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25"/>
   <cols>
     <col min="1" max="1" width="7.625" style="1" customWidth="1"/>
@@ -2563,7 +3439,8 @@
     <col min="8" max="8" width="8.875" style="1" customWidth="1"/>
     <col min="9" max="9" width="13.75" style="1" customWidth="1"/>
     <col min="10" max="10" width="38.75" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="11" max="11" width="52.875" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" spans="1:10">
@@ -2772,7 +3649,7 @@
       </c>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" ht="40.5" spans="1:10">
+    <row r="9" ht="60.75" spans="1:10">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -2796,19 +3673,17 @@
       <c r="I9" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>51</v>
-      </c>
+      <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>53</v>
@@ -2822,7 +3697,7 @@
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J10" s="4"/>
     </row>
@@ -2832,44 +3707,44 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" ht="60.75" spans="1:10">
       <c r="A12" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -2878,19 +3753,19 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J13" s="4"/>
     </row>
@@ -2899,27 +3774,27 @@
         <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2927,25 +3802,25 @@
         <v>19</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" ht="40.5" spans="1:10">
@@ -2953,7 +3828,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -2961,15 +3836,15 @@
         <v>34</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" ht="40.5" spans="1:10">
@@ -2977,19 +3852,19 @@
         <v>10</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>30</v>
@@ -2997,7 +3872,7 @@
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -3006,26 +3881,26 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" ht="40.5" spans="1:10">
@@ -3033,27 +3908,27 @@
         <v>19</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -3062,26 +3937,26 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" ht="40.5" spans="1:10">
@@ -3089,25 +3964,25 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
         <v>41</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" ht="40.5" spans="1:10">
@@ -3116,21 +3991,21 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>41</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J22" s="4"/>
     </row>
@@ -3139,19 +4014,19 @@
         <v>10</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -3159,7 +4034,7 @@
         <v>15</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -3167,25 +4042,25 @@
         <v>19</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" ht="40.5" spans="1:10">
@@ -3193,7 +4068,7 @@
         <v>44</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4" t="s">
@@ -3203,17 +4078,17 @@
         <v>23</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H25" s="4"/>
       <c r="I25" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" ht="60.75" spans="1:10">
@@ -3221,7 +4096,7 @@
         <v>44</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4" t="s">
@@ -3231,17 +4106,17 @@
         <v>23</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" ht="40.5" spans="1:10">
@@ -3250,26 +4125,26 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" ht="40.5" spans="1:10">
@@ -3277,29 +4152,29 @@
         <v>19</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" ht="81" spans="1:10">
@@ -3307,29 +4182,29 @@
         <v>19</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" ht="40.5" spans="1:10">
@@ -3337,29 +4212,29 @@
         <v>10</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H30" s="4"/>
       <c r="I30" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" ht="81" spans="1:10">
@@ -3367,29 +4242,29 @@
         <v>10</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H31" s="4"/>
       <c r="I31" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" ht="40.5" spans="1:10">
@@ -3397,27 +4272,27 @@
         <v>10</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" ht="40.5" spans="1:10">
@@ -3425,27 +4300,27 @@
         <v>10</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -3454,48 +4329,48 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -3504,24 +4379,24 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -3530,19 +4405,19 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J37" s="4"/>
     </row>
@@ -3551,27 +4426,27 @@
         <v>10</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="39" ht="40.5" spans="1:10">
@@ -3579,27 +4454,27 @@
         <v>19</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>41</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -3607,20 +4482,20 @@
         <v>19</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J40" s="4"/>
     </row>
@@ -3629,27 +4504,27 @@
         <v>19</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42" ht="40.5" spans="1:10">
@@ -3657,20 +4532,20 @@
         <v>19</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J42" s="4"/>
     </row>
@@ -3680,26 +4555,26 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H43" s="4"/>
       <c r="I43" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -3708,26 +4583,26 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H44" s="4"/>
       <c r="I44" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45" ht="60.75" spans="1:10">
@@ -3735,27 +4610,27 @@
         <v>19</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H45" s="4"/>
       <c r="I45" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -3763,22 +4638,22 @@
         <v>19</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J46" s="4"/>
     </row>
@@ -3787,29 +4662,29 @@
         <v>10</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H47" s="4"/>
       <c r="I47" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -3818,22 +4693,22 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" ht="40.5" spans="1:10">
@@ -3842,14 +4717,14 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -3857,7 +4732,7 @@
         <v>15</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="50" ht="40.5" spans="1:10">
@@ -3865,27 +4740,27 @@
         <v>19</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H50" s="4"/>
       <c r="I50" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -3893,25 +4768,25 @@
         <v>10</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -3919,22 +4794,22 @@
         <v>44</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -3942,19 +4817,19 @@
         <v>44</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54" ht="40.5" spans="1:10">
@@ -3962,25 +4837,25 @@
         <v>19</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="55" ht="40.5" spans="1:10">
@@ -3988,22 +4863,22 @@
         <v>19</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -4011,25 +4886,25 @@
         <v>10</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -4037,22 +4912,22 @@
         <v>10</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -4060,19 +4935,19 @@
         <v>10</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>31</v>
@@ -4083,22 +4958,22 @@
         <v>19</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="60" ht="81" spans="1:10">
@@ -4106,19 +4981,19 @@
         <v>19</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="61" ht="60.75" spans="1:10">
@@ -4126,22 +5001,22 @@
         <v>19</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="62" ht="40.5" spans="1:10">
@@ -4149,22 +5024,22 @@
         <v>10</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -4172,25 +5047,25 @@
         <v>10</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -4198,19 +5073,19 @@
         <v>10</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -4218,22 +5093,22 @@
         <v>19</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>31</v>
@@ -4241,22 +5116,22 @@
     </row>
     <row r="66" spans="1:10">
       <c r="C66" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>31</v>
@@ -4267,7 +5142,7 @@
         <v>10</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>27</v>
@@ -4276,16 +5151,16 @@
         <v>23</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="68" ht="60.75" spans="1:10">
@@ -4293,7 +5168,7 @@
         <v>19</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>22</v>
@@ -4302,27 +5177,27 @@
         <v>23</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="69" ht="60.75" spans="1:10">
       <c r="F69" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="70" ht="40.5" spans="1:10">
@@ -4330,25 +5205,25 @@
         <v>19</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -4356,22 +5231,22 @@
         <v>19</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -4379,42 +5254,42 @@
         <v>10</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="73" ht="60.75" spans="1:10">
       <c r="C73" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="74" ht="60.75" spans="1:10">
@@ -4422,22 +5297,22 @@
         <v>19</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="75" ht="60.75" spans="1:10">
@@ -4448,19 +5323,19 @@
         <v>11</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="76" ht="40.5" spans="1:10">
@@ -4468,19 +5343,19 @@
         <v>10</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -4488,25 +5363,25 @@
         <v>10</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="78" ht="60.75" spans="1:10">
@@ -4514,19 +5389,19 @@
         <v>10</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="79" ht="60.75" spans="1:10">
@@ -4534,19 +5409,19 @@
         <v>10</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="80" ht="40.5" spans="1:10">
@@ -4554,22 +5429,22 @@
         <v>19</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="81" ht="40.5" spans="1:10">
@@ -4577,25 +5452,25 @@
         <v>19</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -4603,22 +5478,22 @@
         <v>19</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="83" ht="81" spans="1:10">
@@ -4626,25 +5501,25 @@
         <v>19</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -4652,28 +5527,28 @@
         <v>10</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="85" ht="60.75" spans="1:10">
@@ -4681,22 +5556,22 @@
         <v>10</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="86" ht="60.75" spans="1:10">
@@ -4704,22 +5579,22 @@
         <v>19</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="87" ht="81" spans="1:10">
@@ -4727,22 +5602,22 @@
         <v>19</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -4750,22 +5625,22 @@
         <v>19</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="89" ht="40.5" spans="1:10">
@@ -4773,22 +5648,22 @@
         <v>19</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="90" ht="101.25" spans="1:10">
@@ -4796,28 +5671,28 @@
         <v>10</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="91" ht="121.5" spans="1:10">
@@ -4825,25 +5700,25 @@
         <v>19</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="92" ht="101.25" spans="1:10">
@@ -4851,22 +5726,22 @@
         <v>19</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="93" ht="101.25" spans="1:10">
@@ -4874,10 +5749,10 @@
         <v>44</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>44</v>
@@ -4886,13 +5761,13 @@
         <v>23</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="94" ht="40.5" spans="1:10">
@@ -4900,7 +5775,7 @@
         <v>44</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>44</v>
@@ -4909,13 +5784,13 @@
         <v>23</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="95" ht="141.75" spans="1:10">
@@ -4923,28 +5798,28 @@
         <v>19</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="96" ht="101.25" spans="1:10">
@@ -4952,25 +5827,25 @@
         <v>19</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="97" ht="81" spans="1:10">
@@ -4978,28 +5853,28 @@
         <v>19</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="98" ht="40.5" spans="1:10">
@@ -5007,25 +5882,25 @@
         <v>19</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="99" ht="40.5" spans="1:10">
@@ -5033,19 +5908,19 @@
         <v>19</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>15</v>
@@ -5053,7 +5928,7 @@
     </row>
     <row r="100" spans="1:10">
       <c r="C100" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="101" ht="40.5" spans="1:10">
@@ -5061,22 +5936,22 @@
         <v>10</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="102" ht="60.75" spans="1:10">
@@ -5084,22 +5959,22 @@
         <v>10</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="103" ht="60.75" spans="1:10">
@@ -5107,22 +5982,22 @@
         <v>10</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" ht="40.5" spans="1:10">
@@ -5130,25 +6005,25 @@
         <v>10</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" ht="40.5" spans="1:10">
@@ -5156,7 +6031,7 @@
         <v>10</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>27</v>
@@ -5165,16 +6040,16 @@
         <v>34</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="106" ht="40.5" spans="1:10">
@@ -5182,22 +6057,25 @@
         <v>10</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>370</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="107" ht="40.5" spans="1:10">
@@ -5205,25 +6083,25 @@
         <v>10</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="108" ht="40.5" spans="1:10">
@@ -5231,22 +6109,22 @@
         <v>10</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="109" ht="60.75" spans="1:10">
@@ -5254,19 +6132,19 @@
         <v>10</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="110" ht="141.75" spans="1:10">
@@ -5274,22 +6152,22 @@
         <v>10</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="111" ht="40.5" spans="1:10">
@@ -5297,19 +6175,19 @@
         <v>10</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="112" ht="121.5" spans="1:10">
@@ -5317,19 +6195,19 @@
         <v>19</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="113" ht="81" spans="1:10">
@@ -5337,19 +6215,19 @@
         <v>10</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="114" ht="81" spans="1:10">
@@ -5357,19 +6235,19 @@
         <v>19</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="115" ht="121.5" spans="1:10">
@@ -5377,19 +6255,19 @@
         <v>19</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="116" ht="121.5" spans="1:10">
@@ -5397,19 +6275,19 @@
         <v>19</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="117" ht="60.75" spans="1:10">
@@ -5417,22 +6295,22 @@
         <v>19</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="118" ht="121.5" spans="1:10">
@@ -5440,24 +6318,24 @@
         <v>19</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="119" ht="40.5" spans="1:10">
       <c r="C119" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>41</v>
@@ -5468,22 +6346,22 @@
         <v>19</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="121" ht="60.75" spans="1:10">
@@ -5491,25 +6369,25 @@
         <v>10</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="122" ht="60.75" spans="1:10">
@@ -5517,16 +6395,16 @@
         <v>10</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>15</v>
@@ -5537,16 +6415,16 @@
         <v>10</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>15</v>
@@ -5557,25 +6435,25 @@
         <v>10</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="125" ht="81" spans="1:10">
@@ -5583,22 +6461,22 @@
         <v>10</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="126" ht="40.5" spans="1:10">
@@ -5606,22 +6484,22 @@
         <v>10</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="127" ht="40.5" spans="1:10">
@@ -5629,13 +6507,13 @@
         <v>10</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="128" ht="101.25" spans="1:10">
@@ -5643,100 +6521,100 @@
         <v>10</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="129" spans="3:10">
       <c r="C129" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="130" spans="3:10">
       <c r="C130" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="131" spans="3:10">
       <c r="C131" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="132" ht="60.75" spans="3:10">
       <c r="C132" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="133" ht="141.75" spans="3:10">
       <c r="C133" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="134" ht="40.5" spans="3:10">
       <c r="C134" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>41</v>
@@ -5748,140 +6626,140 @@
         <v>15</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="135" spans="3:10">
       <c r="C135" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="136" spans="3:10">
       <c r="C136" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="137" ht="60.75" spans="3:10">
       <c r="C137" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="138" ht="162" spans="3:10">
       <c r="C138" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="139" ht="141.75" spans="3:10">
       <c r="C139" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="140" ht="81" spans="3:10">
       <c r="C140" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="141" ht="40.5" spans="3:10">
       <c r="C141" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="142" ht="40.5" spans="3:10">
       <c r="C142" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>41</v>
@@ -5890,123 +6768,2066 @@
         <v>15</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="143" ht="40.5" spans="3:10">
       <c r="C143" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="144" ht="40.5" spans="3:10">
       <c r="C144" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="145" ht="141.75" spans="3:10">
       <c r="C145" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="146" ht="60.75" spans="3:10">
       <c r="C146" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>41</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="147" ht="40.5" spans="3:10">
       <c r="C147" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="148" spans="3:10">
       <c r="C148" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="149" spans="3:10">
       <c r="C149" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J149" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I149" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J149" s="1" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="150" ht="40.5" spans="3:10">
       <c r="C150" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
+      </c>
+    </row>
+    <row r="151" spans="3:10">
+      <c r="C151" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="152" spans="3:10">
+      <c r="C152" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J152" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="153" ht="60.75" spans="3:10">
+      <c r="C153" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="154" ht="60.75" spans="3:10">
+      <c r="C154" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J154" s="1" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="155" ht="60.75" spans="3:10">
+      <c r="C155" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J155" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="156" spans="3:10">
+      <c r="C156" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="157" ht="60.75" spans="3:10">
+      <c r="C157" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J157" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="158" ht="81" spans="3:10">
+      <c r="C158" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J158" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="159" spans="3:10">
+      <c r="C159" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J159" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="160" spans="3:10">
+      <c r="C160" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J160" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="161" ht="81" spans="2:11">
+      <c r="C161" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J161" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="162" ht="40.5" spans="2:11">
+      <c r="C162" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J162" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="163" ht="141.75" spans="2:11">
+      <c r="C163" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="164" ht="60.75" spans="2:11">
+      <c r="B164" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="165" ht="81" spans="2:11">
+      <c r="C165" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J165" s="1" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="166" ht="40.5" spans="2:11">
+      <c r="C166" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="J166" s="1" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="167" ht="263.25" spans="2:11">
+      <c r="B167" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="J167" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="K167" s="1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="168" ht="40.5" spans="2:11">
+      <c r="C168" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="I168" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J168" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="169" ht="40.5" spans="2:11">
+      <c r="C169" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J169" s="1" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="170" ht="40.5" spans="2:11">
+      <c r="C170" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="171" spans="2:11">
+      <c r="C171" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="J171" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="172" ht="40.5" spans="2:11">
+      <c r="C172" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="173" spans="2:11">
+      <c r="B173" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="I173" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="J173" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="174" ht="40.5" spans="2:11">
+      <c r="B174" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="I174" s="1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="175" ht="40.5" spans="2:11">
+      <c r="B175" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="I175" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="J175" s="1" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="176" ht="40.5" spans="2:11">
+      <c r="B176" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="I176" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="J176" s="1" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="177" ht="40.5" spans="2:10">
+      <c r="B177" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="J177" s="1" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="178" spans="2:10">
+      <c r="B178" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="I178" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="J178" s="1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="179" ht="40.5" spans="2:10">
+      <c r="B179" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="I179" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="J179" s="1" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="180" spans="2:10">
+      <c r="B180" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="I180" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J180" s="1" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="181" ht="81" spans="2:10">
+      <c r="B181" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I181" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J181" s="1" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="182" ht="81" spans="2:10">
+      <c r="B182" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I182" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J182" s="1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="183" ht="81" spans="2:10">
+      <c r="B183" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I183" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J183" s="1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="184" ht="60.75" spans="2:10">
+      <c r="B184" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I184" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J184" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="185" ht="121.5" spans="2:10">
+      <c r="B185" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I185" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J185" s="1" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="186" ht="101.25" spans="2:10">
+      <c r="B186" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I186" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J186" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="187" spans="2:10">
+      <c r="C187" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I187" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="J187" s="1" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="188" ht="60.75" spans="2:10">
+      <c r="C188" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I188" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J188" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="189" ht="60.75" spans="2:10">
+      <c r="B189" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I189" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J189" s="1" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="190" ht="40.5" spans="2:10">
+      <c r="B190" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="J190" s="1" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="191" ht="162" spans="2:10">
+      <c r="B191" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J191" s="1" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="192" ht="40.5" spans="2:10">
+      <c r="B192" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J192" s="1" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10">
+      <c r="B193" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J193" s="1" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="194" ht="60.75" spans="1:10">
+      <c r="B194" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="195" ht="40.5" spans="1:10">
+      <c r="B195" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10">
+      <c r="B196" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10">
+      <c r="C197" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="J197" s="1" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10">
+      <c r="C198" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I198" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J198" s="1" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="199" ht="101.25" spans="1:10">
+      <c r="A199" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="I199" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J199" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="200" ht="40.5" spans="1:10">
+      <c r="A200" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="I200" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J200" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10">
+      <c r="A201" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J201" s="1" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10">
+      <c r="A202" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J202" s="1" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10">
+      <c r="A203" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="I203" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="204" ht="60.75" spans="1:10">
+      <c r="A204" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="I204" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J204" s="1" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="205" ht="40.5" spans="1:10">
+      <c r="A205" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="I205" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J205" s="1" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="206" ht="40.5" spans="1:10">
+      <c r="A206" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="I206" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J206" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="207" ht="40.5" spans="1:10">
+      <c r="A207" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="I207" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J207" s="1" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="208" ht="40.5" spans="1:10">
+      <c r="A208" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="I208" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="J208" s="1" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="209" ht="141.75" spans="1:11">
+      <c r="A209" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="I209" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J209" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="K209" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="210" ht="40.5" spans="1:11">
+      <c r="A210" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J210" s="1" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11">
+      <c r="A211" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J211" s="1" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11">
+      <c r="C212" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J212" s="1" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="213" ht="81" spans="1:11">
+      <c r="C213" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="G213" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="I213" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J213" s="1" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11">
+      <c r="C214" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="J214" s="1" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11">
+      <c r="C215" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J215" s="1" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11">
+      <c r="C216" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J216" s="1" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="217" ht="60.75" spans="1:11">
+      <c r="C217" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J217" s="1" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="218" ht="60.75" spans="1:11">
+      <c r="C218" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J218" s="1" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="219" ht="60.75" spans="1:11">
+      <c r="C219" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I219" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J219" s="1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="220" ht="60.75" spans="1:11">
+      <c r="C220" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="G220" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="J220" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="221" ht="40.5" spans="1:11">
+      <c r="C221" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J221" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="222" ht="60.75" spans="1:11">
+      <c r="C222" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="I222" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="J222" s="1" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="223" ht="40.5" spans="1:11">
+      <c r="C223" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="I223" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J223" s="1" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="224" ht="121.5" spans="1:11">
+      <c r="C224" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="I224" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J224" s="1" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="225" ht="60.75" spans="2:10">
+      <c r="C225" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="I225" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="J225" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="226" ht="40.5" spans="2:10">
+      <c r="C226" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="I226" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="J226" s="1" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="227" ht="40.5" spans="2:10">
+      <c r="C227" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="J227" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="228" ht="121.5" spans="2:10">
+      <c r="C228" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="J228" s="1" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="229" ht="60.75" spans="2:10">
+      <c r="C229" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="F229" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="I229" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="J229" s="1" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="230" ht="121.5" spans="2:10">
+      <c r="C230" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="F230" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="I230" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="J230" s="1" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="231" ht="40.5" spans="2:10">
+      <c r="C231" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="I231" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="232" ht="40.5" spans="2:10">
+      <c r="C232" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="F232" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="I232" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="233" ht="121.5" spans="2:10">
+      <c r="C233" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="I233" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="J233" s="1" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="234" ht="141.75" spans="2:10">
+      <c r="C234" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="I234" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J234" s="1" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="235" ht="40.5" spans="2:10">
+      <c r="C235" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J235" s="1" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="236" ht="81" spans="2:10">
+      <c r="C236" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J236" s="1" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="237" ht="162" spans="2:10">
+      <c r="C237" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J237" s="1" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="238" ht="60.75" spans="2:10">
+      <c r="C238" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F238" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="I238" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="J238" s="1" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="239" ht="121.5" spans="2:10">
+      <c r="C239" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F239" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="I239" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="J239" s="1" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="240" ht="40.5" spans="2:10">
+      <c r="B240" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F240" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I240" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J240" s="1" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="241" spans="2:10">
+      <c r="B241" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F241" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I241" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J241" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="242" ht="60.75" spans="2:10">
+      <c r="B242" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F242" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I242" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J242" s="1" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="243" spans="2:10">
+      <c r="B243" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F243" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="I243" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J243" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="244" ht="40.5" spans="2:10">
+      <c r="B244" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F244" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="I244" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J244" s="1" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="245" ht="101.25" spans="2:10">
+      <c r="C245" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="J245" s="1" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="246" ht="81" spans="2:10">
+      <c r="C246" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="J246" s="1" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="247" ht="81" spans="2:10">
+      <c r="C247" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F247" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I247" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="J247" s="1" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="248" spans="2:10">
+      <c r="C248" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="J248" s="1" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="249" spans="2:10">
+      <c r="C249" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="J249" s="1" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="250" ht="60.75" spans="2:10">
+      <c r="C250" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="F250" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I250" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="J250" s="1" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="251" spans="2:10">
+      <c r="C251" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F251" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I251" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="J251" s="1" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="252" ht="40.5" spans="2:10">
+      <c r="C252" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="J252" s="1" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="253" ht="40.5" spans="2:10">
+      <c r="C253" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F253" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="G253" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="I253" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J253" s="1" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="254" ht="40.5" spans="2:10">
+      <c r="C254" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F254" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="G254" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="I254" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J254" s="1" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="255" spans="2:10">
+      <c r="C255" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F255" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="I255" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="256" ht="40.5" spans="2:10">
+      <c r="C256" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F256" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="G256" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="I256" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J256" s="1" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="257" ht="60.75" spans="3:10">
+      <c r="C257" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F257" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="I257" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J257" s="1" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="258" spans="3:10">
+      <c r="C258" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F258" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I258" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J258" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="259" ht="40.5" spans="3:10">
+      <c r="C259" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J259" s="1" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="260" ht="162" spans="3:10">
+      <c r="C260" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F260" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I260" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="J260" s="1" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="261" ht="243" spans="3:10">
+      <c r="C261" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F261" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="I261" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J261" s="1" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="262" ht="60.75" spans="3:10">
+      <c r="C262" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J262" s="1" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="263" spans="3:10">
+      <c r="C263" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J263" s="1" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="264" ht="121.5" spans="3:10">
+      <c r="C264" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="F264" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="G264" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="I264" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="J264" s="1" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="265" ht="60.75" spans="3:10">
+      <c r="C265" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="F265" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="J265" s="1" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="266" spans="3:10">
+      <c r="C266" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F266" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I266" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J266" s="1" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="267" spans="3:10">
+      <c r="C267" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I267" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J267" s="1" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="268" ht="101.25" spans="3:10">
+      <c r="C268" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J268" s="1" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="269" spans="3:10">
+      <c r="C269" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J269" s="1" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="270" ht="60.75" spans="3:10">
+      <c r="C270" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="F270" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I270" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J270" s="1" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="271" ht="40.5" spans="3:10">
+      <c r="C271" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J271" s="1" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="272" ht="101.25" spans="3:10">
+      <c r="C272" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J272" s="1" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="273" ht="101.25" spans="3:10">
+      <c r="C273" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="I273" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J273" s="1" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="274" spans="3:10">
+      <c r="C274" s="1" t="s">
+        <v>783</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J137" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J268" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6027,18 +8848,18 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="C1" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>495</v>
+        <v>784</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>496</v>
+        <v>785</v>
       </c>
       <c r="C2" s="2">
         <v>4</v>
@@ -6046,10 +8867,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>497</v>
+        <v>786</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>498</v>
+        <v>787</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -6060,10 +8881,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>499</v>
+        <v>788</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -6071,7 +8892,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>500</v>
+        <v>789</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
@@ -6079,7 +8900,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>501</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -6102,40 +8923,40 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="B1" s="1" t="s">
-        <v>502</v>
+        <v>790</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>503</v>
+        <v>791</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>504</v>
+        <v>792</v>
       </c>
     </row>
     <row r="3" ht="141.75" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>505</v>
+        <v>793</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>506</v>
+        <v>794</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>507</v>
+        <v>795</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>506</v>
+        <v>794</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>508</v>
+        <v>796</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6143,10 +8964,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>509</v>
+        <v>797</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>510</v>
+        <v>798</v>
       </c>
     </row>
   </sheetData>
